--- a/1.training_model/supplementary/data tabulation section 2.xlsx
+++ b/1.training_model/supplementary/data tabulation section 2.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2449B891-C960-4473-8E1E-97D6D08545EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B4EA7F-9F68-4D1F-B248-231EFC559C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E9752D00-3F01-4279-B2E7-AB809E1A167F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{E9752D00-3F01-4279-B2E7-AB809E1A167F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="tabulate oiltek_sectio2cluste" sheetId="2" r:id="rId2"/>
+    <sheet name="DRAFT" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet6" sheetId="7" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
+    <sheet name="DRAFT CLUSTER INFO" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="34">
   <si>
     <t>CLUSTER 1</t>
   </si>
@@ -98,13 +101,55 @@
   </si>
   <si>
     <t>CLUSTER 8</t>
+  </si>
+  <si>
+    <t>*** in coding script python (predict_sectioncluster.py), find the line that extract the prediction of equipment type for all the possibilities of the cluster</t>
+  </si>
+  <si>
+    <t>section 2 oiltek</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>PUMP</t>
+  </si>
+  <si>
+    <t>Cluster 1</t>
+  </si>
+  <si>
+    <t>Cluster 2</t>
+  </si>
+  <si>
+    <t>Cluster 3</t>
+  </si>
+  <si>
+    <t>Cluster 4</t>
+  </si>
+  <si>
+    <t>Cluster 5</t>
+  </si>
+  <si>
+    <t>MOTOR</t>
+  </si>
+  <si>
+    <t>ON/OF VALVE</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>CONTROL VALVE</t>
+  </si>
+  <si>
+    <t>HIGH LEVEL SWITCH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,13 +171,79 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CAF50"/>
+        <bgColor rgb="FF33CCCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -147,14 +258,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA9D18E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA9D18E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -698,97 +844,576 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05B4DFF0-33D5-4B7A-854A-72E2D965623E}">
-  <dimension ref="C2:K14"/>
+  <dimension ref="B1:O27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="D2" s="1" t="s">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C3" t="s">
+      <c r="M4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C5" t="s">
+      <c r="O4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>98</v>
+      </c>
+      <c r="D5">
+        <v>88</v>
+      </c>
+      <c r="E5">
+        <v>76</v>
+      </c>
+      <c r="F5">
+        <v>69</v>
+      </c>
+      <c r="G5">
+        <v>56</v>
+      </c>
+      <c r="H5">
+        <v>50</v>
+      </c>
+      <c r="I5">
+        <v>43</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="N5" t="s">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2">
+        <v>94</v>
+      </c>
+      <c r="D6" s="3">
+        <v>88</v>
+      </c>
+      <c r="E6" s="4">
+        <v>76</v>
+      </c>
+      <c r="F6" s="5">
+        <v>63</v>
+      </c>
+      <c r="G6" s="7">
+        <v>38</v>
+      </c>
+      <c r="H6" s="8">
+        <v>55</v>
+      </c>
+      <c r="I6" s="9">
+        <v>50</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="N6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C8" t="s">
+      <c r="O6">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C9" t="s">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2">
+        <v>99</v>
+      </c>
+      <c r="D7">
+        <v>78</v>
+      </c>
+      <c r="E7">
+        <v>75</v>
+      </c>
+      <c r="F7">
+        <v>63</v>
+      </c>
+      <c r="G7">
+        <v>59</v>
+      </c>
+      <c r="H7">
+        <v>44</v>
+      </c>
+      <c r="I7">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>22</v>
+      </c>
+      <c r="N7" t="s">
+        <v>4</v>
+      </c>
+      <c r="O7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2">
+        <v>86</v>
+      </c>
+      <c r="D8">
+        <v>67</v>
+      </c>
+      <c r="E8">
+        <v>51</v>
+      </c>
+      <c r="F8">
+        <v>40</v>
+      </c>
+      <c r="G8" s="6">
+        <v>79</v>
+      </c>
+      <c r="H8">
+        <v>33</v>
+      </c>
+      <c r="I8">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="N8" t="s">
+        <v>5</v>
+      </c>
+      <c r="O8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>90</v>
+      </c>
+      <c r="D9" s="3">
+        <v>86</v>
+      </c>
+      <c r="E9">
+        <v>58</v>
+      </c>
+      <c r="F9">
+        <v>43</v>
+      </c>
+      <c r="G9">
+        <v>35</v>
+      </c>
+      <c r="H9" s="8">
+        <v>77</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9" s="10">
+        <v>60</v>
+      </c>
+      <c r="N9" t="s">
+        <v>6</v>
+      </c>
+      <c r="O9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2">
+        <v>88</v>
+      </c>
+      <c r="D10">
+        <v>78</v>
+      </c>
+      <c r="E10">
+        <v>70</v>
+      </c>
+      <c r="F10">
+        <v>65</v>
+      </c>
+      <c r="G10">
+        <v>57</v>
+      </c>
+      <c r="H10">
+        <v>42</v>
+      </c>
+      <c r="I10">
+        <v>32</v>
+      </c>
+      <c r="J10">
+        <v>13</v>
+      </c>
+      <c r="N10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C10" t="s">
+      <c r="O10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2">
+        <v>91</v>
+      </c>
+      <c r="D11">
+        <v>80</v>
+      </c>
+      <c r="E11">
+        <v>77</v>
+      </c>
+      <c r="F11">
+        <v>65</v>
+      </c>
+      <c r="G11" s="6">
+        <v>85</v>
+      </c>
+      <c r="H11">
+        <v>60</v>
+      </c>
+      <c r="I11">
+        <v>53</v>
+      </c>
+      <c r="J11">
+        <v>24</v>
+      </c>
+      <c r="N11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C11" t="s">
+      <c r="O11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2">
+        <v>87</v>
+      </c>
+      <c r="D12">
+        <v>77</v>
+      </c>
+      <c r="E12">
+        <v>69</v>
+      </c>
+      <c r="F12">
+        <v>60</v>
+      </c>
+      <c r="G12">
+        <v>51</v>
+      </c>
+      <c r="H12">
+        <v>43</v>
+      </c>
+      <c r="I12">
+        <v>38</v>
+      </c>
+      <c r="J12">
+        <v>20</v>
+      </c>
+      <c r="N12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C12" t="s">
+      <c r="O12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2">
+        <v>94</v>
+      </c>
+      <c r="D13">
+        <v>77</v>
+      </c>
+      <c r="E13">
+        <v>69</v>
+      </c>
+      <c r="F13">
+        <v>60</v>
+      </c>
+      <c r="G13">
+        <v>51</v>
+      </c>
+      <c r="H13">
+        <v>43</v>
+      </c>
+      <c r="I13">
+        <v>38</v>
+      </c>
+      <c r="J13">
+        <v>20</v>
+      </c>
+      <c r="N13" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C13" t="s">
+      <c r="O13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2">
+        <v>90</v>
+      </c>
+      <c r="D14">
+        <v>77</v>
+      </c>
+      <c r="E14">
+        <v>69</v>
+      </c>
+      <c r="F14">
+        <v>60</v>
+      </c>
+      <c r="G14">
+        <v>51</v>
+      </c>
+      <c r="H14">
+        <v>43</v>
+      </c>
+      <c r="I14">
+        <v>38</v>
+      </c>
+      <c r="J14">
+        <v>20</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N14" t="s">
+        <v>2</v>
+      </c>
+      <c r="O14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C14" t="s">
+      <c r="C15" s="7">
+        <v>80</v>
+      </c>
+      <c r="D15">
+        <v>77</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+      <c r="F15">
+        <v>42</v>
+      </c>
+      <c r="G15" s="6">
+        <v>97</v>
+      </c>
+      <c r="H15">
+        <v>40</v>
+      </c>
+      <c r="I15">
+        <v>39</v>
+      </c>
+      <c r="J15">
+        <v>24</v>
+      </c>
+      <c r="N15" t="s">
+        <v>5</v>
+      </c>
+      <c r="O15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
         <v>16</v>
+      </c>
+      <c r="C16" s="7">
+        <v>79</v>
+      </c>
+      <c r="D16">
+        <v>70</v>
+      </c>
+      <c r="E16">
+        <v>67</v>
+      </c>
+      <c r="F16">
+        <v>56</v>
+      </c>
+      <c r="G16" s="6">
+        <v>86</v>
+      </c>
+      <c r="H16">
+        <v>50</v>
+      </c>
+      <c r="I16">
+        <v>45</v>
+      </c>
+      <c r="J16">
+        <v>34</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16" t="s">
+        <v>2</v>
+      </c>
+      <c r="O16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="M17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N17" t="s">
+        <v>2</v>
+      </c>
+      <c r="O17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="M18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N18" t="s">
+        <v>7</v>
+      </c>
+      <c r="O18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="N19" t="s">
+        <v>15</v>
+      </c>
+      <c r="O19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="N20" t="s">
+        <v>16</v>
+      </c>
+      <c r="O20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="N21" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="M22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="N23" t="s">
+        <v>2</v>
+      </c>
+      <c r="O23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="M24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N24" t="s">
+        <v>2</v>
+      </c>
+      <c r="O24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="M25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N25" t="s">
+        <v>5</v>
+      </c>
+      <c r="O25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -798,10 +1423,712 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4835DE2F-D909-4EBA-8DA7-8C17F2BF5065}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06E35FEB-6D73-4683-A17D-8D91F6C00848}">
+  <dimension ref="C1:P32"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.36328125" customWidth="1"/>
+    <col min="2" max="2" width="3.81640625" customWidth="1"/>
+    <col min="3" max="3" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.08984375" customWidth="1"/>
+    <col min="5" max="5" width="12.26953125" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" customWidth="1"/>
+    <col min="10" max="10" width="5.90625" customWidth="1"/>
+    <col min="15" max="15" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="N1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+      <c r="O2">
+        <v>2</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="1"/>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3">
+        <v>2</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
+        <v>4</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="M6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6">
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="M7" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7">
+        <f>SUM(N2:N6)</f>
+        <v>14</v>
+      </c>
+      <c r="O7">
+        <f t="shared" ref="O7:P7" si="0">SUM(O2:O6)</f>
+        <v>10</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+    </row>
+    <row r="10" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+    </row>
+    <row r="12" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+    </row>
+    <row r="14" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+    </row>
+    <row r="15" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+    </row>
+    <row r="16" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="M18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="E4:I32">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>E4=MAX($C4:$G4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01828EFE-E3C2-4C2C-A424-D392316382D7}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4835DE2F-D909-4EBA-8DA7-8C17F2BF5065}">
+  <dimension ref="B2:D23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="21.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C658A0D-E104-4514-939C-0189735DAFD0}">
+  <dimension ref="B2:E7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>